--- a/Analysis/Sensitivity_alpha_sweep_gptoss.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_gptoss.xlsx
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.04068000000000001</v>
+        <v>0.03248</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03845999999999999</v>
+        <v>0.03795999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.33334</v>
+        <v>0.34052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.66462</v>
+        <v>0.66562</v>
       </c>
       <c r="J2" t="n">
         <v>195</v>
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2724799999999999</v>
+        <v>0.23418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.29076</v>
+        <v>0.25078</v>
       </c>
       <c r="H3" t="n">
-        <v>0.47386</v>
+        <v>0.46462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7651199999999999</v>
+        <v>0.76308</v>
       </c>
       <c r="J3" t="n">
         <v>195</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8974400000000001</v>
+        <v>0.8047910769230768</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9113599999999999</v>
+        <v>0.8194900512820513</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9173</v>
+        <v>0.8246088205128205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9812799999999999</v>
+        <v>0.8933590769230768</v>
       </c>
       <c r="J4" t="n">
-        <v>171.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.04545999999999999</v>
+        <v>0.00716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04462000000000001</v>
+        <v>0.007700000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.34254</v>
+        <v>0.31384</v>
       </c>
       <c r="I5" t="n">
-        <v>0.67282</v>
+        <v>0.64308</v>
       </c>
       <c r="J5" t="n">
         <v>195</v>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.27044</v>
+        <v>0.2225800000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2841</v>
+        <v>0.23232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.48104</v>
+        <v>0.44614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7630799999999999</v>
+        <v>0.7405200000000001</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.89122</v>
+        <v>0.7924926153846155</v>
       </c>
       <c r="G7" t="n">
-        <v>0.90502</v>
+        <v>0.8087142564102564</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92078</v>
+        <v>0.8102605128205129</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9789999999999999</v>
+        <v>0.8933502564102564</v>
       </c>
       <c r="J7" t="n">
-        <v>171.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -727,16 +727,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.04409999999999999</v>
+        <v>0.03042</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04206</v>
+        <v>0.0359</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33538</v>
+        <v>0.33846</v>
       </c>
       <c r="I8" t="n">
-        <v>0.66976</v>
+        <v>0.6636</v>
       </c>
       <c r="J8" t="n">
         <v>195</v>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.27454</v>
+        <v>0.2335</v>
       </c>
       <c r="G9" t="n">
-        <v>0.29284</v>
+        <v>0.25026</v>
       </c>
       <c r="H9" t="n">
-        <v>0.47694</v>
+        <v>0.46358</v>
       </c>
       <c r="I9" t="n">
-        <v>0.76616</v>
+        <v>0.76308</v>
       </c>
       <c r="J9" t="n">
         <v>195</v>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.8982199999999999</v>
+        <v>0.8068469743589743</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9126</v>
+        <v>0.8210316923076924</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91848</v>
+        <v>0.8246088205128205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.98246</v>
+        <v>0.8964248205128204</v>
       </c>
       <c r="J10" t="n">
-        <v>171.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11">
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.04271999999999999</v>
+        <v>0.03386</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04102</v>
+        <v>0.03999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33434</v>
+        <v>0.34154</v>
       </c>
       <c r="I11" t="n">
-        <v>0.66872</v>
+        <v>0.6666800000000001</v>
       </c>
       <c r="J11" t="n">
         <v>195</v>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.27452</v>
+        <v>0.23692</v>
       </c>
       <c r="G12" t="n">
-        <v>0.29234</v>
+        <v>0.25284</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4769200000000001</v>
+        <v>0.46362</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7651199999999999</v>
+        <v>0.76308</v>
       </c>
       <c r="J12" t="n">
         <v>195</v>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.89978</v>
+        <v>0.8088964102564102</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9155000000000001</v>
+        <v>0.8266572307692309</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9208000000000001</v>
+        <v>0.8297381538461538</v>
       </c>
       <c r="I13" t="n">
-        <v>0.98594</v>
+        <v>0.8984523076923077</v>
       </c>
       <c r="J13" t="n">
-        <v>171.6</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.04476000000000001</v>
+        <v>0.03112</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0446</v>
+        <v>0.03796</v>
       </c>
       <c r="H14" t="n">
         <v>0.33846</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6738600000000001</v>
+        <v>0.6635799999999998</v>
       </c>
       <c r="J14" t="n">
         <v>195</v>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.27796</v>
+        <v>0.24106</v>
       </c>
       <c r="G15" t="n">
-        <v>0.29588</v>
+        <v>0.25644</v>
       </c>
       <c r="H15" t="n">
-        <v>0.48206</v>
+        <v>0.45844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.77024</v>
+        <v>0.76922</v>
       </c>
       <c r="J15" t="n">
         <v>195</v>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8958199999999999</v>
+        <v>0.8136828717948719</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91428</v>
+        <v>0.8312968205128206</v>
       </c>
       <c r="H16" t="n">
-        <v>0.915</v>
+        <v>0.8369356923076923</v>
       </c>
       <c r="I16" t="n">
-        <v>0.98594</v>
+        <v>0.9015255384615385</v>
       </c>
       <c r="J16" t="n">
-        <v>171.6</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
